--- a/src/src/main/resources/template/UserAccountImport_Template.xlsx
+++ b/src/src/main/resources/template/UserAccountImport_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212670825\Desktop\APM\Git\hc-apm-web\src\src\main\webapp\portal\uaa\userAccount\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCA2815-638A-4FB5-A2DC-30710618B7B9}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F592CF49-4638-465B-AFC7-E8E6FE1740AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>所属集团</t>
   </si>
@@ -76,6 +76,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>新增医院</t>
@@ -85,7 +86,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>A</t>
     </r>
@@ -99,6 +100,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>新增层级</t>
@@ -108,7 +110,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -117,6 +119,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>科室</t>
@@ -126,7 +129,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -137,6 +140,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>新增层级</t>
@@ -146,7 +150,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -155,6 +159,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>科室</t>
@@ -164,7 +169,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -175,6 +180,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>新增层级</t>
@@ -184,7 +190,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -193,6 +199,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>科室</t>
@@ -202,7 +209,7 @@
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>1</t>
     </r>
@@ -293,13 +300,17 @@
   </si>
   <si>
     <t>标签</t>
+  </si>
+  <si>
+    <t>停用?*</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -310,13 +321,26 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -491,7 +515,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
@@ -1613,24 +1637,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IX2"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
+  <dimension ref="A1:IY2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.44140625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="14.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.42578125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.77734375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.6640625" style="1" customWidth="1"/>
-    <col min="14" max="17" width="30" style="1" customWidth="1"/>
-    <col min="18" max="18" width="32.6640625" style="1" customWidth="1"/>
-    <col min="19" max="258" width="8.77734375" style="1" customWidth="1"/>
+    <col min="11" max="13" width="8.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.7109375" style="1" customWidth="1"/>
+    <col min="15" max="18" width="30" style="1" customWidth="1"/>
+    <col min="19" max="19" width="32.7109375" style="1" customWidth="1"/>
+    <col min="20" max="259" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:258" ht="30.75" customHeight="1">
+    <row r="1" spans="1:259" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1668,25 +1692,27 @@
         <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="7"/>
-      <c r="T1" s="10"/>
+      <c r="T1" s="7"/>
       <c r="U1" s="10"/>
       <c r="V1" s="10"/>
       <c r="W1" s="10"/>
@@ -1924,9 +1950,10 @@
       <c r="IU1" s="10"/>
       <c r="IV1" s="10"/>
       <c r="IW1" s="10"/>
-      <c r="IX1" s="12"/>
-    </row>
-    <row r="2" spans="1:258" ht="34.5" customHeight="1">
+      <c r="IX1" s="10"/>
+      <c r="IY1" s="12"/>
+    </row>
+    <row r="2" spans="1:259" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -1961,20 +1988,22 @@
       <c r="L2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="11"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="9"/>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
@@ -2212,9 +2241,11 @@
       <c r="IU2" s="11"/>
       <c r="IV2" s="11"/>
       <c r="IW2" s="11"/>
-      <c r="IX2" s="13"/>
+      <c r="IX2" s="11"/>
+      <c r="IY2" s="13"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
   <headerFooter>
@@ -2226,117 +2257,117 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:IR23"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="108.6640625" style="1" customWidth="1"/>
-    <col min="2" max="252" width="8.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="108.7109375" style="1" customWidth="1"/>
+    <col min="2" max="252" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="13.8" customHeight="1">
+    <row r="1" spans="1:1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="13.8" customHeight="1">
+    <row r="2" spans="1:1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
     </row>
-    <row r="3" spans="1:1" ht="16.05" customHeight="1">
+    <row r="3" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="16.05" customHeight="1">
+    <row r="4" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="16.05" customHeight="1">
+    <row r="5" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="16.05" customHeight="1">
+    <row r="6" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="16.05" customHeight="1">
+    <row r="7" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="16.05" customHeight="1">
+    <row r="8" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="16.05" customHeight="1">
+    <row r="9" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="16.05" customHeight="1">
+    <row r="10" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="16.05" customHeight="1">
+    <row r="11" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" ht="13.8" customHeight="1">
+    <row r="12" spans="1:1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="12" customHeight="1">
+    <row r="13" spans="1:1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="17"/>
     </row>
-    <row r="14" spans="1:1" ht="16.05" customHeight="1">
+    <row r="14" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="16.05" customHeight="1">
+    <row r="15" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="16.05" customHeight="1">
+    <row r="16" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16.05" customHeight="1">
+    <row r="17" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16.05" customHeight="1">
+    <row r="18" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16.05" customHeight="1">
+    <row r="19" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16.05" customHeight="1">
+    <row r="20" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16.05" customHeight="1">
+    <row r="21" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16.05" customHeight="1">
+    <row r="22" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="13.5" customHeight="1">
+    <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
@@ -2346,8 +2377,9 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A12:A13"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/src/src/main/resources/template/UserAccountImport_Template.xlsx
+++ b/src/src/main/resources/template/UserAccountImport_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503310146\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503282840\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F592CF49-4638-465B-AFC7-E8E6FE1740AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D623AD5B-3B92-49AE-8953-EE9C958035CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="datalist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>所属集团</t>
   </si>
@@ -305,12 +305,18 @@
     <t>停用?*</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>资产分类</t>
+  </si>
+  <si>
+    <t>资产分类非必填(租户开启资产分类值为资产分类的编码例如    ：01-01,01-02多项用,号分割 )</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -363,7 +369,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -476,11 +482,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -513,6 +532,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1637,8 +1657,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IY2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:IZ2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
@@ -1649,12 +1669,12 @@
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
     <col min="11" max="13" width="8.7109375" style="1" customWidth="1"/>
     <col min="14" max="14" width="24.7109375" style="1" customWidth="1"/>
-    <col min="15" max="18" width="30" style="1" customWidth="1"/>
-    <col min="19" max="19" width="32.7109375" style="1" customWidth="1"/>
-    <col min="20" max="259" width="8.7109375" style="1" customWidth="1"/>
+    <col min="15" max="19" width="30" style="1" customWidth="1"/>
+    <col min="20" max="20" width="32.7109375" style="1" customWidth="1"/>
+    <col min="21" max="260" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:259" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:260" ht="30.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1710,10 +1730,12 @@
         <v>47</v>
       </c>
       <c r="S1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="7"/>
-      <c r="U1" s="10"/>
+      <c r="U1" s="7"/>
       <c r="V1" s="10"/>
       <c r="W1" s="10"/>
       <c r="X1" s="10"/>
@@ -1951,9 +1973,10 @@
       <c r="IV1" s="10"/>
       <c r="IW1" s="10"/>
       <c r="IX1" s="10"/>
-      <c r="IY1" s="12"/>
-    </row>
-    <row r="2" spans="1:259" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="IY1" s="10"/>
+      <c r="IZ1" s="12"/>
+    </row>
+    <row r="2" spans="1:260" ht="34.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
@@ -2002,9 +2025,9 @@
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="11"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="9"/>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
@@ -2242,7 +2265,8 @@
       <c r="IV2" s="11"/>
       <c r="IW2" s="11"/>
       <c r="IX2" s="11"/>
-      <c r="IY2" s="13"/>
+      <c r="IY2" s="11"/>
+      <c r="IZ2" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2256,120 +2280,125 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IR23"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:IR24"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="108.7109375" style="1" customWidth="1"/>
     <col min="2" max="252" width="8.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="13.9" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="13.9" customHeight="1">
       <c r="A2" s="15"/>
     </row>
-    <row r="3" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="13.9" customHeight="1">
       <c r="A12" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" ht="12" customHeight="1">
       <c r="A13" s="17"/>
     </row>
-    <row r="14" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="16.149999999999999" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="13.5" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="12.75" customHeight="1">
+      <c r="A24" s="18" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
